--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136380752</v>
       </c>
       <c r="B19" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136377751</v>
       </c>
       <c r="B25" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>136380847</v>
       </c>
       <c r="B26" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136381090</v>
       </c>
       <c r="B27" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136381593</v>
       </c>
       <c r="B28" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136383972</v>
       </c>
       <c r="B29" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136385942</v>
       </c>
       <c r="B30" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136381157</v>
       </c>
       <c r="B34" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>136382055</v>
       </c>
       <c r="B35" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>136383951</v>
       </c>
       <c r="B36" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136387470</v>
       </c>
       <c r="B37" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>136384553</v>
       </c>
       <c r="B38" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>136377437</v>
       </c>
       <c r="B39" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136381242</v>
       </c>
       <c r="B42" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136382105</v>
       </c>
       <c r="B43" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>136382144</v>
       </c>
       <c r="B44" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>136385918</v>
       </c>
       <c r="B45" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136380752</v>
       </c>
       <c r="B19" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136377751</v>
       </c>
       <c r="B25" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>136380847</v>
       </c>
       <c r="B26" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136381090</v>
       </c>
       <c r="B27" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136381593</v>
       </c>
       <c r="B28" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136383972</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136385942</v>
       </c>
       <c r="B30" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136381157</v>
       </c>
       <c r="B34" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>136382055</v>
       </c>
       <c r="B35" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>136383951</v>
       </c>
       <c r="B36" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136387470</v>
       </c>
       <c r="B37" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136381242</v>
       </c>
       <c r="B42" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136382105</v>
       </c>
       <c r="B43" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>136382144</v>
       </c>
       <c r="B44" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>136385918</v>
       </c>
       <c r="B45" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>136381781</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136382782</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136383003</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>136383126</v>
       </c>
       <c r="B7" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>136385902</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136386118</v>
       </c>
       <c r="B9" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136387141</v>
       </c>
       <c r="B10" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>136387286</v>
       </c>
       <c r="B11" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136392867</v>
       </c>
       <c r="B12" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136378941</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136387804</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>136380752</v>
       </c>
       <c r="B19" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>136377751</v>
       </c>
       <c r="B25" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>136380847</v>
       </c>
       <c r="B26" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136381090</v>
       </c>
       <c r="B27" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136381593</v>
       </c>
       <c r="B28" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136383972</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136385942</v>
       </c>
       <c r="B30" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136381157</v>
       </c>
       <c r="B34" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>136382055</v>
       </c>
       <c r="B35" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>136383951</v>
       </c>
       <c r="B36" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>136387470</v>
       </c>
       <c r="B37" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>136382388</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136381242</v>
       </c>
       <c r="B42" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136382105</v>
       </c>
       <c r="B43" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>136382144</v>
       </c>
       <c r="B44" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>136385918</v>
       </c>
       <c r="B45" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2026 artfynd.xlsx
+++ b/artfynd/A 34096-2026 artfynd.xlsx
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jens Johansen, Olle Kvarnbäck, Petter Brorson Edh, Maja Karlsson</t>
+          <t>Maja Karlsson, Petter Brorson Edh, Olle Kvarnbäck, Jens Johansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
